--- a/Documentation/VELORA_V1_Product_Backlog.xlsx
+++ b/Documentation/VELORA_V1_Product_Backlog.xlsx
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">

--- a/Documentation/VELORA_V1_Product_Backlog.xlsx
+++ b/Documentation/VELORA_V1_Product_Backlog.xlsx
@@ -1859,7 +1859,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">

--- a/Documentation/VELORA_V1_Product_Backlog.xlsx
+++ b/Documentation/VELORA_V1_Product_Backlog.xlsx
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">

--- a/Documentation/VELORA_V1_Product_Backlog.xlsx
+++ b/Documentation/VELORA_V1_Product_Backlog.xlsx
@@ -2095,7 +2095,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">

--- a/Documentation/VELORA_V1_Product_Backlog.xlsx
+++ b/Documentation/VELORA_V1_Product_Backlog.xlsx
@@ -2047,7 +2047,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">

--- a/Documentation/VELORA_V1_Product_Backlog.xlsx
+++ b/Documentation/VELORA_V1_Product_Backlog.xlsx
@@ -1906,7 +1906,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>To Do</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
